--- a/C_fibonacci/graficas.xlsx
+++ b/C_fibonacci/graficas.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\C_fibonacci\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194C1CBC-3971-4C04-9604-AE254CDB67EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -14,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -49,8 +58,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -66,6 +76,1698 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>recursivo: pasos</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$A$1:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$B$1:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>453</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>57291</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7049123</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>866988831</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.00E+00">
+                  <c:v>106633000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E511-4A90-AA8D-5FE71BD5FD79}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="453718872"/>
+        <c:axId val="453719200"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="453718872"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="453719200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="453719200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="453718872"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>recursivo: tiempos</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.5925460398809569E-2"/>
+          <c:y val="0.21075075075075075"/>
+          <c:w val="0.89736667828982752"/>
+          <c:h val="0.63790830200279014"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>recursivo: tiempos</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$A$1:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$C$1:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.6679999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>199.99700000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7CEF-4396-9AA2-E2389BB92091}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="453718872"/>
+        <c:axId val="453719200"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="453718872"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="453719200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="453719200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="453718872"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>recursivo/memoizacion: tiempos</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.5925460398809569E-2"/>
+          <c:y val="0.21075075075075075"/>
+          <c:w val="0.89736667828982752"/>
+          <c:h val="0.63790830200279014"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>recursivo/memoizacion: tiempos</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$F$1:$F$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$H$1:$H$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-902F-4BAE-B5F6-C869728C01FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="453718872"/>
+        <c:axId val="453719200"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="453718872"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="453719200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="453719200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="453718872"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>recursivo/memoizacion: pasos</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.5925460398809569E-2"/>
+          <c:y val="0.21075075075075075"/>
+          <c:w val="0.89736667828982752"/>
+          <c:h val="0.63790830200279014"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>recursivo/memoizacion: pasos</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$F$1:$F$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$G$1:$G$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>155</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D2B9-487E-B48F-591E8608822F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="453718872"/>
+        <c:axId val="453719200"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="453718872"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="453719200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="453719200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="453718872"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A66C2B5D-C3FE-4FE7-B1E1-1D6EAD3D6EC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C35F1BAE-0C55-4865-BDC2-2EEC7ED7F0D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC48F295-B175-4167-9CAF-BBF326E39DF7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>297180</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD60EF0B-D800-4905-B8B5-5DBD4B7DD7CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +2032,563 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>10</v>
+      </c>
+      <c r="B1">
+        <v>453</v>
+      </c>
+      <c r="C1">
+        <v>0</v>
+      </c>
+      <c r="F1">
+        <v>10</v>
+      </c>
+      <c r="G1">
+        <v>29</v>
+      </c>
+      <c r="H1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>57291</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>17</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>30</v>
+      </c>
+      <c r="B3">
+        <v>7049123</v>
+      </c>
+      <c r="C3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>19</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>40</v>
+      </c>
+      <c r="B4">
+        <v>866988831</v>
+      </c>
+      <c r="C4">
+        <v>1.6679999999999999</v>
+      </c>
+      <c r="F4">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>21</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>50</v>
+      </c>
+      <c r="B5" s="1">
+        <v>106633000000</v>
+      </c>
+      <c r="C5">
+        <v>199.99700000000001</v>
+      </c>
+      <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>23</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>27</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>24</v>
+      </c>
+      <c r="G8">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>26</v>
+      </c>
+      <c r="G9">
+        <v>31</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>28</v>
+      </c>
+      <c r="G10">
+        <v>33</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <v>30</v>
+      </c>
+      <c r="G11">
+        <v>35</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <v>32</v>
+      </c>
+      <c r="G12">
+        <v>37</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <v>34</v>
+      </c>
+      <c r="G13">
+        <v>39</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <v>36</v>
+      </c>
+      <c r="G14">
+        <v>41</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <v>38</v>
+      </c>
+      <c r="G15">
+        <v>43</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>40</v>
+      </c>
+      <c r="G16">
+        <v>45</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>42</v>
+      </c>
+      <c r="G17">
+        <v>47</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>44</v>
+      </c>
+      <c r="G18">
+        <v>49</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <v>46</v>
+      </c>
+      <c r="G19">
+        <v>51</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <v>48</v>
+      </c>
+      <c r="G20">
+        <v>53</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <v>50</v>
+      </c>
+      <c r="G21">
+        <v>55</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F22">
+        <v>52</v>
+      </c>
+      <c r="G22">
+        <v>57</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <v>54</v>
+      </c>
+      <c r="G23">
+        <v>59</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F24">
+        <v>56</v>
+      </c>
+      <c r="G24">
+        <v>61</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <v>58</v>
+      </c>
+      <c r="G25">
+        <v>63</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <v>60</v>
+      </c>
+      <c r="G26">
+        <v>65</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <v>62</v>
+      </c>
+      <c r="G27">
+        <v>67</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <v>64</v>
+      </c>
+      <c r="G28">
+        <v>69</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F29">
+        <v>66</v>
+      </c>
+      <c r="G29">
+        <v>71</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F30">
+        <v>68</v>
+      </c>
+      <c r="G30">
+        <v>73</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F31">
+        <v>70</v>
+      </c>
+      <c r="G31">
+        <v>75</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F32">
+        <v>72</v>
+      </c>
+      <c r="G32">
+        <v>77</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F33">
+        <v>74</v>
+      </c>
+      <c r="G33">
+        <v>79</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F34">
+        <v>76</v>
+      </c>
+      <c r="G34">
+        <v>81</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F35">
+        <v>78</v>
+      </c>
+      <c r="G35">
+        <v>83</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F36">
+        <v>80</v>
+      </c>
+      <c r="G36">
+        <v>85</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F37">
+        <v>82</v>
+      </c>
+      <c r="G37">
+        <v>87</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F38">
+        <v>84</v>
+      </c>
+      <c r="G38">
+        <v>89</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F39">
+        <v>86</v>
+      </c>
+      <c r="G39">
+        <v>91</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F40">
+        <v>88</v>
+      </c>
+      <c r="G40">
+        <v>93</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F41">
+        <v>90</v>
+      </c>
+      <c r="G41">
+        <v>95</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F42">
+        <v>92</v>
+      </c>
+      <c r="G42">
+        <v>97</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F43">
+        <v>94</v>
+      </c>
+      <c r="G43">
+        <v>101</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F44">
+        <v>96</v>
+      </c>
+      <c r="G44">
+        <v>109</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F45">
+        <v>98</v>
+      </c>
+      <c r="G45">
+        <v>143</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F46">
+        <v>100</v>
+      </c>
+      <c r="G46">
+        <v>155</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>